--- a/reports/빅딜/history/2026-09-25/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-09-25/빅딜_training_mgf_report.xlsx
@@ -231,7 +231,7 @@
     <t>5경 985조 128억 1537만</t>
   </si>
   <si>
-    <t>셀린느2군 IN 300위분들   귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -309,7 +309,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>6경 6141조 4,657억 3,898만</t>
+    <t>6경 6141조 4657억 3898만</t>
   </si>
   <si>
     <t>2</t>
@@ -327,7 +327,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>2경 8747조 2,524억 6,858만</t>
+    <t>2경 8747조 2524억 6858만</t>
   </si>
   <si>
     <t>3</t>
@@ -345,7 +345,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 630조 4,441억 5,868만</t>
+    <t>1경 630조 4441억 5868만</t>
   </si>
   <si>
     <t>4</t>
@@ -363,7 +363,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>6327조 503억 4,939만</t>
+    <t>6327조 503억 4939만</t>
   </si>
   <si>
     <t>5</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%B1%A0</t>
   </si>
   <si>
-    <t>4842조 8,830억 3,283만</t>
+    <t>4842조 8830억 3283만</t>
   </si>
   <si>
     <t>6</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%84%EA%B5%AC</t>
   </si>
   <si>
-    <t>4808조 4,650억 4,072만</t>
+    <t>4808조 4650억 4072만</t>
   </si>
   <si>
     <t>7</t>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=GOD%EB%82%A0%EB%91%90</t>
   </si>
   <si>
-    <t>4260조 3,079억 8,728만</t>
+    <t>4260조 3079억 8728만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3846조 9,002억 873만</t>
+    <t>3846조 9002억 873만</t>
   </si>
   <si>
     <t>9</t>
@@ -429,7 +429,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>3339조 7,819억 8,470만</t>
+    <t>3339조 7819억 8470만</t>
   </si>
   <si>
     <t>10</t>
@@ -441,7 +441,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B0%8C%EB%B0%94%EB%A6%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>2938조 9,566억 7,745만</t>
+    <t>2938조 9566억 7745만</t>
   </si>
   <si>
     <t>11</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%B8%8C%ED%8F%AC%ED%8B%B0</t>
   </si>
   <si>
-    <t>2805조 7,388억 7,122만</t>
+    <t>2805조 7388억 7122만</t>
   </si>
   <si>
     <t>12</t>
@@ -468,7 +468,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>2367조 6,141억 542만</t>
+    <t>2367조 6141억 542만</t>
   </si>
   <si>
     <t>13</t>
@@ -480,7 +480,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>2171조 2,630억 8,147만</t>
+    <t>2171조 2630억 8147만</t>
   </si>
   <si>
     <t>14</t>
@@ -495,7 +495,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>1860조 7,967억 6,835만</t>
+    <t>1860조 7967억 6835만</t>
   </si>
   <si>
     <t>15</t>
@@ -510,7 +510,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>1752조 4,338억 1,823만</t>
+    <t>1752조 4338억 1823만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>1692조 2,004억 4,089만</t>
+    <t>1692조 2004억 4089만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8A%98%ED%95%9C%EA%B7%B8%EB%8A%98</t>
   </si>
   <si>
-    <t>1574조 1,606억 2,965만</t>
+    <t>1574조 1606억 2965만</t>
   </si>
   <si>
     <t>18</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%95%98%EB%A1%9C%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>1536조 9,319억 6,510만</t>
+    <t>1536조 9319억 6510만</t>
   </si>
   <si>
     <t>19</t>
@@ -561,7 +561,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>1224조 930억 2,497만</t>
+    <t>1224조 930억 2497만</t>
   </si>
   <si>
     <t>20</t>
@@ -573,7 +573,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%A6%BF</t>
   </si>
   <si>
-    <t>1114조 7,266억 7,195만</t>
+    <t>1114조 7266억 7195만</t>
   </si>
   <si>
     <t>21</t>
@@ -591,7 +591,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1038조 1,690억 5,557만</t>
+    <t>1038조 1690억 5557만</t>
   </si>
   <si>
     <t>22</t>
@@ -603,7 +603,7 @@
     <t>https://mgf.gg/contents/character.php?n=v%EB%B0%95%ED%9A%A8%EC%8B%A0v</t>
   </si>
   <si>
-    <t>1037조 494억 3,376만</t>
+    <t>1037조 494억 3376만</t>
   </si>
   <si>
     <t>23</t>
@@ -615,7 +615,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%98%A4</t>
   </si>
   <si>
-    <t>985조 3,833억 8,106만</t>
+    <t>985조 3833억 8106만</t>
   </si>
   <si>
     <t>24</t>
@@ -630,7 +630,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>948조 2,787억 2,895만</t>
+    <t>948조 2787억 2895만</t>
   </si>
   <si>
     <t>25</t>
@@ -642,7 +642,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>862조 9,981억 2,406만</t>
+    <t>862조 9981억 2406만</t>
   </si>
   <si>
     <t>26</t>
@@ -654,7 +654,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%9C%BC%EB%86%8D</t>
   </si>
   <si>
-    <t>782조 5,974억 6,272만</t>
+    <t>782조 5974억 6272만</t>
   </si>
   <si>
     <t>27</t>
@@ -666,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%87%B8</t>
   </si>
   <si>
-    <t>545조 140억 3,857만</t>
+    <t>545조 140억 3857만</t>
   </si>
   <si>
     <t>28</t>
@@ -681,7 +681,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>501조 2,685억 7,899만</t>
+    <t>501조 2685억 7899만</t>
   </si>
   <si>
     <t>29</t>
@@ -693,7 +693,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A6%AC%EB%AF%B8%EC%BF%B5</t>
   </si>
   <si>
-    <t>496조 7,292억 3,016만</t>
+    <t>496조 7292억 3016만</t>
   </si>
   <si>
     <t>30</t>
@@ -705,7 +705,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EB%B0%B0%EB%B6%88%EB%9F%AC%EC%9A%94</t>
   </si>
   <si>
-    <t>438조 6,576억 9,723만</t>
+    <t>438조 6576억 9723만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%EC%9C%A0%EB%AC%B4</t>
@@ -714,7 +714,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 1162조 1,533억 1,870만</t>
+    <t>1경 1162조 1533억 1870만</t>
   </si>
   <si>
     <t>무곽</t>
@@ -723,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BD</t>
   </si>
   <si>
-    <t>1경 185조 1,642억 4,847만</t>
+    <t>1경 185조 1642억 4847만</t>
   </si>
   <si>
     <t>형팡팡이</t>
@@ -732,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%ED%8C%A1%ED%8C%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>4996조 5,941억 3,100만</t>
+    <t>4996조 5941억 3100만</t>
   </si>
   <si>
     <t>2번째캐릭</t>
@@ -741,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=2%EB%B2%88%EC%A7%B8%EC%BA%90%EB%A6%AD</t>
   </si>
   <si>
-    <t>3247조 628억 2,570만</t>
+    <t>3247조 628억 2570만</t>
   </si>
   <si>
     <t>붉은모자</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%89%EC%9D%80%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>3233조 3,396억 9,304만</t>
+    <t>3233조 3396억 9304만</t>
   </si>
   <si>
     <t>장뱁새</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3031조 5,264억 7,495만</t>
+    <t>3031조 5264억 7495만</t>
   </si>
   <si>
     <t>꽁꽁냉법</t>
@@ -768,7 +768,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%83%89%EB%B2%95</t>
   </si>
   <si>
-    <t>2333조 4,544억 8,833만</t>
+    <t>2333조 4544억 8833만</t>
   </si>
   <si>
     <t>테토일남</t>
@@ -780,7 +780,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>1985조 8,710억 9,334만</t>
+    <t>1985조 8710억 9334만</t>
   </si>
   <si>
     <t>뚜기파파</t>
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B8%B0%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>1746조 6,215억 912만</t>
+    <t>1746조 6215억 912만</t>
   </si>
   <si>
     <t>브네</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%84%A4</t>
   </si>
   <si>
-    <t>1584조 5,973억 6,962만</t>
+    <t>1584조 5973억 6962만</t>
   </si>
   <si>
     <t>라쥬르</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A5%AC%EB%A5%B4</t>
   </si>
   <si>
-    <t>1528조 947억 6,864만</t>
+    <t>1528조 947억 6864만</t>
   </si>
   <si>
     <t>빙율</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EC%9C%A8</t>
   </si>
   <si>
-    <t>1193조 4,056억 8,035만</t>
+    <t>1193조 4056억 8035만</t>
   </si>
   <si>
     <t>33세배장호</t>
@@ -834,7 +834,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EC%A0%B9%EC%A0%81</t>
   </si>
   <si>
-    <t>1018조 1,956억 6,161만</t>
+    <t>1018조 1956억 6161만</t>
   </si>
   <si>
     <t>재미있게놀래</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%AF%B8%EC%9E%88%EA%B2%8C%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>960조 3,899억 5,166만</t>
+    <t>960조 3899억 5166만</t>
   </si>
   <si>
     <t>가덴</t>
@@ -852,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%8D%B4</t>
   </si>
   <si>
-    <t>856조 2,582억 8,336만</t>
+    <t>856조 2582억 8336만</t>
   </si>
   <si>
     <t>정기휴므</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EA%B8%B0%ED%9C%B4%EB%AF%80</t>
   </si>
   <si>
-    <t>826조 7,863억 3,978만</t>
+    <t>826조 7863억 3978만</t>
   </si>
   <si>
     <t>최빵쭈</t>
@@ -873,7 +873,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>783조 5,993억 9,157만</t>
+    <t>783조 5993억 9157만</t>
   </si>
   <si>
     <t>타뤽</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%A4%BD</t>
   </si>
   <si>
-    <t>759조 1,590억 8,137만</t>
+    <t>759조 1590억 8137만</t>
   </si>
   <si>
     <t>무르스</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%A5%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>722조 8,101억 454만</t>
+    <t>722조 8101억 454만</t>
   </si>
   <si>
     <t>새벽놀래</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EB%86%80%EB%9E%98</t>
   </si>
   <si>
-    <t>721조 9,101억 319만</t>
+    <t>721조 9101억 319만</t>
   </si>
   <si>
     <t>채황새</t>
@@ -918,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AD%ED%82%A4%EB%A3%A8%ED%82%A4</t>
   </si>
   <si>
-    <t>536조 2,111억 8,984만</t>
+    <t>536조 2111억 8984만</t>
   </si>
   <si>
     <t>저기휴무</t>
@@ -927,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>520조 5,128억</t>
+    <t>520조 5128억</t>
   </si>
   <si>
     <t>넬샷</t>
@@ -936,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%AC%EC%83%B7</t>
   </si>
   <si>
-    <t>494조 6,391억 6,864만</t>
+    <t>494조 6391억 6864만</t>
   </si>
   <si>
     <t>박도란</t>
@@ -945,7 +945,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%8F%84%EB%9E%80</t>
   </si>
   <si>
-    <t>423조 4,561억 9,991만</t>
+    <t>423조 4561억 9991만</t>
   </si>
   <si>
     <t>장기휴무</t>
@@ -954,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B8%B0%ED%9C%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>410조 8,040억 472만</t>
+    <t>410조 8040억 472만</t>
   </si>
   <si>
     <t>뿌앵뿌앵</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EC%95%B5%EB%BF%8C%EC%95%B5</t>
   </si>
   <si>
-    <t>392조 7,676억 5,327만</t>
+    <t>392조 7676억 5327만</t>
   </si>
   <si>
     <t>윤빵쭈</t>
@@ -975,7 +975,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>279조 8,923억 8,669만</t>
+    <t>279조 8923억 8669만</t>
   </si>
   <si>
     <t>냥홍이</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%ED%99%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>268조 9,505억 6,629만</t>
+    <t>268조 9505억 6629만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>8188조 1,046억 1,273만</t>
+    <t>8188조 1046억 1273만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
   </si>
   <si>
-    <t>6992조 3,764억 4,633만</t>
+    <t>6992조 3764억 4633만</t>
   </si>
   <si>
     <t>협의</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4402조 1,032억 4,015만</t>
+    <t>4402조 1032억 4015만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4094조 124억 4,985만</t>
+    <t>4094조 124억 4985만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
   </si>
   <si>
-    <t>3303조 6,174억 3,840만</t>
+    <t>3303조 6174억 3840만</t>
   </si>
   <si>
     <t>타개</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2988조 9,066억 1,886만</t>
+    <t>2988조 9066억 1886만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2424조 9,978억 2,159만</t>
+    <t>2424조 9978억 2159만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -1056,7 +1056,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>2269조 6,121억 182만</t>
+    <t>2290조 8654억 1226만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2279조 9226억 7885만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -1065,16 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2224조 5,091억 9,296만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2182조 5,730억 5,749만</t>
+    <t>2224조 5091억 9296만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -1083,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>1978조 8,306억 8,833만</t>
+    <t>1978조 8306억 8833만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4,812억 8,418만</t>
+    <t>1831조 4812억 8418만</t>
   </si>
   <si>
     <t>온백</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1814조 2,226억 6,845만</t>
+    <t>1814조 2226억 6845만</t>
   </si>
   <si>
     <t>파울</t>
@@ -1110,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1766조 7,006억 9,923만</t>
+    <t>1766조 7006억 9923만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5,749억 9,080만</t>
+    <t>1596조 5749억 9080만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -1128,13 +1128,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1240조 6,809억 9,149만</t>
+    <t>1240조 6809억 9149만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1213조 7,003억 6,444만</t>
+    <t>1213조 7003억 6444만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -1143,7 +1143,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>1149조 8,047억 287만</t>
+    <t>1149조 8047억 287만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -1152,7 +1152,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9,888억 5,564만</t>
+    <t>1091조 9888억 5564만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -1161,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4,181억 3,112만</t>
+    <t>1050조 4181억 3112만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -1170,7 +1170,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5,975만</t>
+    <t>1046조 865억 5975만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1033조 7,202억 5,586만</t>
+    <t>1033조 7202억 5586만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5,704억 3,498만</t>
+    <t>1015조 5704억 3498만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -1197,7 +1197,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5,234억 8,229만</t>
+    <t>799조 5234억 8229만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -1206,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5,685억 5,174만</t>
+    <t>796조 5685억 5174만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -1215,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>765조 9,289억 1,162만</t>
+    <t>765조 9289억 1162만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -1224,7 +1224,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>747조 6,533억 1,496만</t>
+    <t>747조 6533억 1496만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>665조 2,579억 6,198만</t>
+    <t>665조 2579억 6198만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -1242,7 +1242,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>649조 5,527억 6,316만</t>
+    <t>649조 5527억 6316만</t>
   </si>
   <si>
     <t>빵후</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>277조 36억 4,103만</t>
+    <t>277조 36억 4103만</t>
   </si>
   <si>
     <t>전액할부</t>
@@ -1260,7 +1260,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%95%A1%ED%95%A0%EB%B6%80</t>
   </si>
   <si>
-    <t>1경 556조 6,511억 5,477만</t>
+    <t>1경 556조 6511억 5477만</t>
   </si>
   <si>
     <t>사랑향</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%96%A5</t>
   </si>
   <si>
-    <t>7984조 7,938억 2,458만</t>
+    <t>7984조 7938억 2458만</t>
   </si>
   <si>
     <t>힐폿</t>
@@ -1287,7 +1287,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%80%EC%A0%84</t>
   </si>
   <si>
-    <t>3668조 9,031억 8,187만</t>
+    <t>3668조 9031억 8187만</t>
   </si>
   <si>
     <t>숭타이준</t>
@@ -1296,13 +1296,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%ED%83%80%EC%9D%B4%EC%A4%80</t>
   </si>
   <si>
-    <t>3001조 7,702억 6,620만</t>
+    <t>3001조 7702억 6620만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%9C%ED%8F%BF</t>
   </si>
   <si>
-    <t>2598조 7,115억 1,793만</t>
+    <t>2598조 7115억 1793만</t>
   </si>
   <si>
     <t>뻑걸</t>
@@ -1311,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B1%B8</t>
   </si>
   <si>
-    <t>1867조 5,966억 1,163만</t>
+    <t>1867조 5966억 1163만</t>
   </si>
   <si>
     <t>뮬이</t>
@@ -1320,7 +1320,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1618조 7,801억 3,460만</t>
+    <t>1618조 7801억 3460만</t>
   </si>
   <si>
     <t>지존빵수</t>
@@ -1329,7 +1329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%B5%EC%88%98</t>
   </si>
   <si>
-    <t>1610조 953억 6,364만</t>
+    <t>1610조 953억 6364만</t>
   </si>
   <si>
     <t>야키산</t>
@@ -1338,7 +1338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%82%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>1576조 9,887억 2,494만</t>
+    <t>1576조 9887억 2494만</t>
   </si>
   <si>
     <t>문제적남자</t>
@@ -1347,7 +1347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%A0%9C%EC%A0%81%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>1447조 754억 2,073만</t>
+    <t>1447조 754억 2073만</t>
   </si>
   <si>
     <t>탱폿</t>
@@ -1356,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%ED%8F%BF</t>
   </si>
   <si>
-    <t>1399조 9,788억 4,010만</t>
+    <t>1399조 9788억 4010만</t>
   </si>
   <si>
     <t>우즈2텐겐</t>
@@ -1365,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A6%882%ED%85%90%EA%B2%90</t>
   </si>
   <si>
-    <t>1317조 4,439억 6,807만</t>
+    <t>1317조 4439억 6807만</t>
   </si>
   <si>
     <t>아이리쉬</t>
@@ -1374,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>1252조 7,283억 7,526만</t>
+    <t>1252조 7283억 7526만</t>
   </si>
   <si>
     <t>독스케</t>
@@ -1383,7 +1383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%8A%A4%EC%BC%80</t>
   </si>
   <si>
-    <t>1150조 9,844억 1,359만</t>
+    <t>1150조 9844억 1359만</t>
   </si>
   <si>
     <t>우월별하</t>
@@ -1392,7 +1392,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9B%94%EB%B3%84%ED%95%98</t>
   </si>
   <si>
-    <t>1032조 7,712억 9,061만</t>
+    <t>1032조 7712억 9061만</t>
   </si>
   <si>
     <t>화둥에불낸년</t>
@@ -1401,7 +1401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EB%91%A5%EC%97%90%EB%B6%88%EB%82%B8%EB%85%84</t>
   </si>
   <si>
-    <t>1004조 9,588억 8,909만</t>
+    <t>1004조 9588억 8909만</t>
   </si>
   <si>
     <t>이게용</t>
@@ -1410,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B2%8C%EC%9A%A9</t>
   </si>
   <si>
-    <t>978조 4,612억 6,155만</t>
+    <t>978조 4612억 6155만</t>
   </si>
   <si>
     <t>기똥찬벌레</t>
@@ -1419,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%98%A5%EC%B0%AC%EB%B2%8C%EB%A0%88</t>
   </si>
   <si>
-    <t>951조 8,281억 4,925만</t>
+    <t>951조 8281억 4925만</t>
   </si>
   <si>
     <t>매화로이</t>
@@ -1428,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A1%9C%EC%9D%B4</t>
   </si>
   <si>
-    <t>888조 3,912억 9,246만</t>
+    <t>888조 3912억 9246만</t>
   </si>
   <si>
     <t>JJuna</t>
@@ -1437,7 +1437,7 @@
     <t>https://mgf.gg/contents/character.php?n=JJuna</t>
   </si>
   <si>
-    <t>820조 1,636억 7,645만</t>
+    <t>820조 1636억 7645만</t>
   </si>
   <si>
     <t>에프람</t>
@@ -1446,7 +1446,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%ED%94%84%EB%9E%8C</t>
   </si>
   <si>
-    <t>762조 4,036억 3,352만</t>
+    <t>762조 4036억 3352만</t>
   </si>
   <si>
     <t>콜리셰마드르</t>
@@ -1455,7 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%85%B0%EB%A7%88%EB%93%9C%EB%A5%B4</t>
   </si>
   <si>
-    <t>722조 8,675억 2,990만</t>
+    <t>722조 8675억 2990만</t>
   </si>
   <si>
     <t>난센</t>
@@ -1464,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EC%84%BC</t>
   </si>
   <si>
-    <t>712조 8,834억 5,919만</t>
+    <t>712조 8834억 5919만</t>
   </si>
   <si>
     <t>구도류</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%8F%84%EB%A5%98</t>
   </si>
   <si>
-    <t>597조 4,814억 267만</t>
+    <t>597조 4814억 267만</t>
   </si>
   <si>
     <t>조단23</t>
@@ -1482,7 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%8B%A823</t>
   </si>
   <si>
-    <t>547조 1,752억 7,480만</t>
+    <t>547조 1752억 7480만</t>
   </si>
   <si>
     <t>유채아버지</t>
@@ -1491,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%B1%84%EC%95%84%EB%B2%84%EC%A7%80</t>
   </si>
   <si>
-    <t>539조 4,690억 5,456만</t>
+    <t>539조 4690억 5456만</t>
   </si>
   <si>
     <t>아콩린</t>
@@ -1500,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BD%A9%EB%A6%B0</t>
   </si>
   <si>
-    <t>531조 5,593억 3,139만</t>
+    <t>531조 5593억 3139만</t>
   </si>
   <si>
     <t>별루루</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A3%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>424조 6,674억 8,815만</t>
+    <t>424조 6674억 8815만</t>
   </si>
   <si>
     <t>꺄꽁</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%84%EA%BD%81</t>
   </si>
   <si>
-    <t>7135조 6,187억 3,211만</t>
+    <t>7278조 8334억 8539만</t>
   </si>
   <si>
     <t>별쌥</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A5</t>
   </si>
   <si>
-    <t>5960조 7,320억 2,376만</t>
+    <t>5960조 7320억 2376만</t>
   </si>
   <si>
     <t>진욱이에요</t>
@@ -1536,13 +1536,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9A%B1%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>4550조 1,468억 5,509만</t>
+    <t>4550조 1468억 5509만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A5%B4%EB%AA%AC</t>
   </si>
   <si>
-    <t>3646조 653억 8,697만</t>
+    <t>3646조 653억 8697만</t>
   </si>
   <si>
     <t>낭만황금망치</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%ED%99%A9%EA%B8%88%EB%A7%9D%EC%B9%98</t>
   </si>
   <si>
-    <t>3488조 4,591억 2,770만</t>
+    <t>3489조 5165억 7352만</t>
   </si>
   <si>
     <t>김슴줌1</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B4%EC%A4%8C1</t>
   </si>
   <si>
-    <t>3270조 2,257억 1,209만</t>
+    <t>3270조 2257억 1209만</t>
   </si>
   <si>
     <t>천달</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%AC</t>
   </si>
   <si>
-    <t>2717조 9,833억 6,552만</t>
+    <t>2717조 9833억 6552만</t>
   </si>
   <si>
     <t>호두와감자</t>
@@ -1578,7 +1578,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%91%90%EC%99%80%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>2525조 8,587억 8,102만</t>
+    <t>2525조 8587억 8102만</t>
+  </si>
+  <si>
+    <t>활용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>2013조 908억 8266만</t>
   </si>
   <si>
     <t>쿠댜</t>
@@ -1587,16 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EB%8C%9C</t>
   </si>
   <si>
-    <t>1916조 9,415억 6,270만</t>
-  </si>
-  <si>
-    <t>활용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%9C%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>1867조 7,074억 9,904만</t>
+    <t>1966조 5445억 7393만</t>
   </si>
   <si>
     <t>뚜징</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EC%A7%95</t>
   </si>
   <si>
-    <t>1806조 9,134억 8,019만</t>
+    <t>1806조 9134억 8019만</t>
   </si>
   <si>
     <t>별곡</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%A1</t>
   </si>
   <si>
-    <t>969조 8,456억 4,768만</t>
+    <t>969조 8456억 4768만</t>
   </si>
   <si>
     <t>까쿠미</t>
@@ -1623,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EC%BF%A0%EB%AF%B8</t>
   </si>
   <si>
-    <t>861조 9,064억 5,984만</t>
+    <t>861조 9064억 5984만</t>
   </si>
   <si>
     <t>턍ol</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%84%8Dol</t>
   </si>
   <si>
-    <t>788조 6,038억 6,835만</t>
+    <t>788조 6038억 6835만</t>
   </si>
   <si>
     <t>동래</t>
@@ -1641,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9E%98</t>
   </si>
   <si>
-    <t>788조 3,697억 1,727만</t>
+    <t>788조 3697억 1727만</t>
   </si>
   <si>
     <t>별쌤</t>
@@ -1650,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%8C%A4</t>
   </si>
   <si>
-    <t>738조 5,918억 5,801만</t>
+    <t>738조 5918억 5801만</t>
   </si>
   <si>
     <t>게렬곰</t>
@@ -1659,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EB%A0%AC%EA%B3%B0</t>
   </si>
   <si>
-    <t>729조 1,853억 3,020만</t>
+    <t>729조 1853억 3020만</t>
   </si>
   <si>
     <t>초이레</t>
@@ -1668,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%9D%B4%EB%A0%88</t>
   </si>
   <si>
-    <t>651조 5,939억 4,000만</t>
+    <t>651조 5939억 4000만</t>
   </si>
   <si>
     <t>띠우</t>
@@ -1686,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%84%EC%B1%B0</t>
   </si>
   <si>
-    <t>473조 8,542억 7,621만</t>
+    <t>475조 4236억 4624만</t>
   </si>
   <si>
     <t>민족고대감자</t>
@@ -1695,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%A1%B1%EA%B3%A0%EB%8C%80%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>447조 5,787억 6,359만</t>
+    <t>447조 5787억 6359만</t>
   </si>
   <si>
     <t>쿠까미</t>
@@ -1704,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EA%B9%8C%EB%AF%B8</t>
   </si>
   <si>
-    <t>442조 874억 8,170만</t>
+    <t>442조 874억 8170만</t>
   </si>
   <si>
     <t>승아의하루</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%95%84%EC%9D%98%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>419조 8,392억 5,458만</t>
+    <t>419조 8392억 5458만</t>
   </si>
   <si>
     <t>왕단단이</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EB%8B%A8%EB%8B%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>374조 1,106억 1,593만</t>
+    <t>374조 1106억 1593만</t>
   </si>
   <si>
     <t>택Ol</t>
@@ -1731,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9DOl</t>
   </si>
   <si>
-    <t>343조 8,584억 7,876만</t>
+    <t>343조 8584억 7876만</t>
   </si>
   <si>
     <t>08217</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=08217</t>
   </si>
   <si>
-    <t>328조 6,713억 6,296만</t>
+    <t>328조 6713억 6296만</t>
   </si>
   <si>
     <t>루이쥔</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%9D%B4%EC%A5%94</t>
   </si>
   <si>
-    <t>312조 422억 7,493만</t>
+    <t>312조 422억 7493만</t>
   </si>
   <si>
     <t>툼스데이</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%BC%EC%8A%A4%EB%8D%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>285조 1,117억 8,099만</t>
+    <t>285조 1117억 8099만</t>
   </si>
   <si>
     <t>꾸현</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%ED%98%84</t>
   </si>
   <si>
-    <t>88조 3,966억 6,293만</t>
+    <t>88조 3966억 6293만</t>
   </si>
   <si>
     <t>달갸뤼</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EA%B0%B8%EB%A4%BC</t>
   </si>
   <si>
-    <t>73조 4,903억 3,576만</t>
+    <t>73조 4903억 3576만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -1785,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>9713조 4,850억 8,781만</t>
+    <t>9713조 4850억 8781만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -1794,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>6465조 5,267억 4,688만</t>
+    <t>6465조 5267억 4688만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -1803,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>3686조 3,442억 6,715만</t>
+    <t>3686조 3442억 6715만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4,643억 9,612만</t>
+    <t>3586조 4643억 9612만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8,887억 4,598만</t>
+    <t>3469조 8887억 4598만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8,452억 3,773만</t>
+    <t>2483조 8452억 3773만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2417조 4,217억 703만</t>
+    <t>2431조 544억 4930만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -1848,13 +1848,13 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4,587억 3,879만</t>
+    <t>1905조 4587억 3879만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>1831조 3,912억 3,225만</t>
+    <t>1831조 3912억 3225만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -1863,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>1825조 2,398억 5,085만</t>
+    <t>1825조 2398억 5085만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -1872,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>1697조 755억 7,134만</t>
+    <t>1697조 755억 7134만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -1881,7 +1881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
   </si>
   <si>
-    <t>1259조 8,128억 5,685만</t>
+    <t>1259조 8128억 5685만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1890,7 +1890,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2,431억 2,633만</t>
+    <t>1058조 2431억 2633만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1899,7 +1899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1052조 9,891억 7,693만</t>
+    <t>1052조 9891억 7693만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -1908,7 +1908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1006조 7,349억 1,730만</t>
+    <t>1006조 7349억 1730만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1917,7 +1917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>987조 2,843억 9,824만</t>
+    <t>987조 2843억 9824만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>926조 2,055억 4,066만</t>
+    <t>928조 8138억 6047만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>914조 9,534억 4,237만</t>
+    <t>914조 9534억 4237만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>864조 6,290억 5,998만</t>
+    <t>864조 6290억 5998만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1953,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1,285억 7,637만</t>
+    <t>560조 1285억 7637만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -1962,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>532조 1,581억 8,976만</t>
+    <t>532조 1581억 8976만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1971,7 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5,489억 3,382만</t>
+    <t>459조 5489억 3382만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -1980,7 +1980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8,785억 9,592만</t>
+    <t>420조 8785억 9592만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1989,7 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>410조 5,852억 7,919만</t>
+    <t>410조 5852억 7919만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4,821억 9,681만</t>
+    <t>372조 4821억 9681만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -2007,7 +2007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
   </si>
   <si>
-    <t>275조 6,869억 3,523만</t>
+    <t>275조 6869억 3523만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -2016,7 +2016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9,325억 1,140만</t>
+    <t>249조 9325억 1140만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -2025,7 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>245조 4,859억 3,395만</t>
+    <t>245조 4859억 3395만</t>
   </si>
   <si>
     <t>교주만두</t>
@@ -2034,7 +2034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%90%EC%A3%BC%EB%A7%8C%EB%91%90</t>
   </si>
   <si>
-    <t>6경 4821조 8,677억 1,103만</t>
+    <t>6경 4821조 8677억 1103만</t>
   </si>
   <si>
     <t>할바이</t>
@@ -2046,7 +2046,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>231조 2,461억 1,057만</t>
+    <t>231조 2461억 1057만</t>
   </si>
   <si>
     <t>섹밍</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B9%EB%B0%8D</t>
   </si>
   <si>
-    <t>211조 4,498억 8,225만</t>
+    <t>211조 4498억 8225만</t>
   </si>
   <si>
     <t>대구남성</t>
@@ -2067,7 +2067,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>73조 3,158억 3,342만</t>
+    <t>73조 3158억 3342만</t>
   </si>
   <si>
     <t>코잉코잉</t>
@@ -2079,7 +2079,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>39조 280억 1,146만</t>
+    <t>39조 280억 1146만</t>
   </si>
   <si>
     <t>토벤숍이</t>
@@ -2088,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%B2%A4%EC%88%8D%EC%9D%B4</t>
   </si>
   <si>
-    <t>36조 4,537억 6,794만</t>
+    <t>36조 4537억 6794만</t>
   </si>
   <si>
     <t>낭랑28세</t>
@@ -2097,7 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%9E%9128%EC%84%B8</t>
   </si>
   <si>
-    <t>36조 3,976억 1,339만</t>
+    <t>36조 3976억 1339만</t>
   </si>
   <si>
     <t>빵신궁</t>
@@ -2106,7 +2106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%8B%A0%EA%B6%81</t>
   </si>
   <si>
-    <t>30조 7,181억 324만</t>
+    <t>30조 7181억 324만</t>
   </si>
   <si>
     <t>오스띤</t>
@@ -2115,7 +2115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%8A%A4%EB%9D%A4</t>
   </si>
   <si>
-    <t>29조 9,499억 3,058만</t>
+    <t>29조 9499억 3058만</t>
   </si>
   <si>
     <t>밀초크코</t>
@@ -2124,7 +2124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EC%B4%88%ED%81%AC%EC%BD%94</t>
   </si>
   <si>
-    <t>28조 1,153억 4,015만</t>
+    <t>28조 1153억 4015만</t>
   </si>
   <si>
     <t>마키맛키마</t>
@@ -2136,7 +2136,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>27조 2,464억 4,277만</t>
+    <t>27조 2464억 4277만</t>
   </si>
   <si>
     <t>킬혁</t>
@@ -2145,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%AC%ED%98%81</t>
   </si>
   <si>
-    <t>25조 4,433억 6,581만</t>
+    <t>25조 4433억 6581만</t>
   </si>
   <si>
     <t>썬콜우체국</t>
@@ -2157,7 +2157,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>25조 787억 2,808만</t>
+    <t>25조 787억 2808만</t>
   </si>
   <si>
     <t>문보겨엉</t>
@@ -2169,7 +2169,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>24조 1,864억 5,790만</t>
+    <t>24조 1864억 5790만</t>
   </si>
   <si>
     <t>고통받는갈비</t>
@@ -2178,7 +2178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%ED%86%B5%EB%B0%9B%EB%8A%94%EA%B0%88%EB%B9%84</t>
   </si>
   <si>
-    <t>23조 9,956억 4,822만</t>
+    <t>23조 9956억 4822만</t>
   </si>
   <si>
     <t>씅놈</t>
@@ -2187,7 +2187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%94%85%EB%86%88</t>
   </si>
   <si>
-    <t>22조 1,653억 9,791만</t>
+    <t>22조 1653억 9791만</t>
   </si>
   <si>
     <t>배렛나루왁서</t>
@@ -2196,7 +2196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A0%9B%EB%82%98%EB%A3%A8%EC%99%81%EC%84%9C</t>
   </si>
   <si>
-    <t>20조 6,218억 5,190만</t>
+    <t>20조 6218억 5190만</t>
   </si>
   <si>
     <t>땡요나퐁</t>
@@ -2205,7 +2205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A1%EC%9A%94%EB%82%98%ED%90%81</t>
   </si>
   <si>
-    <t>20조 2,598억 1,813만</t>
+    <t>20조 2598억 1813만</t>
   </si>
   <si>
     <t>썬콜법사ss</t>
@@ -2214,7 +2214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%ACss</t>
   </si>
   <si>
-    <t>19조 4,439억 6,528만</t>
+    <t>19조 4439억 6528만</t>
   </si>
   <si>
     <t>포디케이</t>
@@ -2223,13 +2223,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%94%94%EC%BC%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>9조 5,884억 9,293만</t>
+    <t>9조 5884억 9293만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%82%A4%EB%B9%84%ED%82%A4</t>
   </si>
   <si>
-    <t>6조 3,603억 7,229만</t>
+    <t>6조 3603억 7229만</t>
   </si>
   <si>
     <t>경기도인</t>
@@ -2241,7 +2241,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>5조 6,702억 2,764만</t>
+    <t>5조 6702억 2764만</t>
   </si>
   <si>
     <t>즈나니</t>
@@ -2253,7 +2253,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>3조 2,857억 8,721만</t>
+    <t>3조 2857억 8721만</t>
   </si>
 </sst>
 </file>
@@ -2986,7 +2986,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4031,7 +4031,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5076,7 +5076,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5388,7 +5388,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>131</v>
@@ -5420,7 +5420,7 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>131</v>
@@ -6121,7 +6121,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7133,7 +7133,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7445,10 +7445,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>518</v>
@@ -7477,10 +7477,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>521</v>
@@ -8177,7 +8177,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9156,7 +9156,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
